--- a/data/Type1/species by biomass/ES_Cantabrian_NIA_Station_21.xlsx
+++ b/data/Type1/species by biomass/ES_Cantabrian_NIA_Station_21.xlsx
@@ -1,33 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Dropbox\0_IEO\Ciencia\ICES\WKBENTH4\5_OUTPUTS\Type_1\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9CA56B-B50E-41DF-85FA-F918BE4A59FE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadata and protocols" sheetId="1" r:id="rId1"/>
-    <sheet name="Species information" sheetId="3" r:id="rId2"/>
-    <sheet name="Time series information" sheetId="4" r:id="rId3"/>
+    <sheet name="Metadata and protocols" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Time series information" sheetId="4" state="visible" r:id="rId3"/>
+    <sheet name="Species information" sheetId="3" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>cl_name</t>
   </si>
@@ -300,23 +288,212 @@
   </si>
   <si>
     <t>2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type_2_year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">station_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">depth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">area_sample</t>
+  </si>
+  <si>
+    <t xml:space="preserve">replicates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">substrate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">assessment_unit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_abundance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_biomass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">richness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rel Margalef div (dens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rel Margalef div (biom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SoS_2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">area_sampled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_number_individuals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_biomass_correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rel.margalef.div.(dens)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rel.margalef.div.(biom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_BQI_2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_Station_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otter_trawl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offshore circalittoral sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.06325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circalittoral sand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES_Cantabrian_NIA_Station_21.xlsx_2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIA_STATION_21_2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -342,9 +519,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,11 +816,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -652,7 +828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -660,7 +836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -668,7 +844,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -676,7 +852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -684,7 +860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -692,7 +868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -700,7 +876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -708,7 +884,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -716,7 +892,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -724,7 +900,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -732,7 +908,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -740,7 +916,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -748,7 +924,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -756,7 +932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -764,7 +940,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -772,7 +948,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -780,7 +956,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -788,7 +964,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -796,7 +972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -804,7 +980,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -812,7 +988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -820,7 +996,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -835,11 +1011,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I86"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -868,26 +1044,26 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>40</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>2013</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>100946</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>5.4702660040000005E-4</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>3.8291862030000001E-3</v>
       </c>
       <c r="H2" t="s">
@@ -897,26 +1073,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>40</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>2013</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>103743</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>7.2936880059999994E-5</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>5.2879238039999995E-4</v>
       </c>
       <c r="H3" t="s">
@@ -926,26 +1102,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>40</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>2013</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>107236</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>3.829186203E-4</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>2.5527908019999999E-3</v>
       </c>
       <c r="H4" t="s">
@@ -955,26 +1131,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>40</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>2013</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>107342</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>1.823422001E-5</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>1.823422001E-5</v>
       </c>
       <c r="H5" t="s">
@@ -984,26 +1160,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>2013</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>123867</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>1.2763954009999999E-4</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>1.9145931020000001E-3</v>
       </c>
       <c r="H6" t="s">
@@ -1013,26 +1189,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>2013</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>124929</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1.823422001E-5</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>1.823422001E-5</v>
       </c>
       <c r="H7" t="s">
@@ -1042,26 +1218,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>40</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>2013</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>125131</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>3.6468440029999997E-5</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>5.4702660039999997E-5</v>
       </c>
       <c r="H8" t="s">
@@ -1071,26 +1247,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>40</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>2013</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>130464</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>1.823422001E-5</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>1.823422001E-5</v>
       </c>
       <c r="H9" t="s">
@@ -1100,26 +1276,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>2013</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="s">
         <v>29</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>141101</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>3.6468440029999997E-5</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>2.1789892920000001E-2</v>
       </c>
       <c r="H10" t="s">
@@ -1129,26 +1305,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>2013</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>149898</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>1.823422001E-5</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>3.4645018029999999E-3</v>
       </c>
       <c r="H11" t="s">
@@ -1158,26 +1334,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>2013</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>532031</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>1.823422001E-5</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>1.011999211E-2</v>
       </c>
       <c r="H12" t="s">
@@ -1187,26 +1363,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>2013</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="s">
         <v>29</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>1670329</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>1.823422001E-5</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>1.7322509009999999E-3</v>
       </c>
       <c r="H13" t="s">
@@ -1216,26 +1392,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>2014</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>100946</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>7.1605144989999995E-4</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>1.1016176149999999E-2</v>
       </c>
       <c r="H14" t="s">
@@ -1245,26 +1421,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>40</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>2014</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="s">
         <v>29</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>103743</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>1.8360293589999998E-5</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>7.3441174350000004E-5</v>
       </c>
       <c r="H15" t="s">
@@ -1274,26 +1450,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>40</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>2014</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="s">
         <v>29</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>106834</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>1.8360293589999998E-5</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>1.8360293589999998E-5</v>
       </c>
       <c r="H16" t="s">
@@ -1303,26 +1479,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>2014</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="s">
         <v>29</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>107236</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>5.5080880770000005E-4</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>3.8923822410000001E-3</v>
       </c>
       <c r="H17" t="s">
@@ -1332,26 +1508,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>40</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>2014</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>123803</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>9.1801467940000005E-5</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>6.9585512700000001E-3</v>
       </c>
       <c r="H18" t="s">
@@ -1361,26 +1537,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>40</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>2014</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="s">
         <v>29</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>123867</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>1.101617615E-4</v>
       </c>
-      <c r="G19">
+      <c r="G19" t="n">
         <v>1.0648970280000001E-3</v>
       </c>
       <c r="H19" t="s">
@@ -1390,26 +1566,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>40</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>2014</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>124048</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1.8360293589999998E-5</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>1.101617615E-4</v>
       </c>
       <c r="H20" t="s">
@@ -1419,26 +1595,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>40</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>2014</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="s">
         <v>29</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>125131</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>5.691691012E-4</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>1.817669065E-3</v>
       </c>
       <c r="H21" t="s">
@@ -1448,26 +1624,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>40</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>2014</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="s">
         <v>29</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>138922</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1.8360293589999998E-5</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>1.23013967E-3</v>
       </c>
       <c r="H22" t="s">
@@ -1477,26 +1653,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>40</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>2014</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>141115</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>3.6720587179999997E-5</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>1.378858048E-2</v>
       </c>
       <c r="H23" t="s">
@@ -1506,26 +1682,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>40</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="n">
         <v>2014</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>29</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>149898</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>1.8360293589999998E-5</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>2.2399558179999998E-3</v>
       </c>
       <c r="H24" t="s">
@@ -1535,26 +1711,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>40</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="n">
         <v>2015</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>100946</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>7.2077266829999998E-5</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>6.3067608479999997E-4</v>
       </c>
       <c r="H25" t="s">
@@ -1564,26 +1740,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>40</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="n">
         <v>2015</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="s">
         <v>29</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>107236</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1.801931671E-5</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>2.7028975060000002E-4</v>
       </c>
       <c r="H26" t="s">
@@ -1593,26 +1769,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>40</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="n">
         <v>2015</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>119936</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>1.801931671E-5</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>1.801931671E-5</v>
       </c>
       <c r="H27" t="s">
@@ -1622,26 +1798,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>40</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="n">
         <v>2015</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="s">
         <v>29</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>123867</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>5.4057950119999998E-5</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>1.171255586E-3</v>
       </c>
       <c r="H28" t="s">
@@ -1651,26 +1827,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>40</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="n">
         <v>2015</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="s">
         <v>29</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>125131</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>3.6038633420000001E-5</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>3.6038633420000001E-5</v>
       </c>
       <c r="H29" t="s">
@@ -1680,26 +1856,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>40</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="n">
         <v>2015</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="s">
         <v>29</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>138922</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>1.801931671E-5</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>5.585988179E-4</v>
       </c>
       <c r="H30" t="s">
@@ -1709,26 +1885,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>40</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="n">
         <v>2015</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="s">
         <v>29</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>141101</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>1.801931671E-5</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>1.030704916E-2</v>
       </c>
       <c r="H31" t="s">
@@ -1738,26 +1914,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>40</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="n">
         <v>2016</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="s">
         <v>29</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>100946</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>3.6090190829999997E-5</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>3.609019083E-4</v>
       </c>
       <c r="H32" t="s">
@@ -1767,26 +1943,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>40</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="n">
         <v>2016</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="s">
         <v>29</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>107236</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>3.6090190829999997E-5</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>2.7067643119999999E-4</v>
       </c>
       <c r="H33" t="s">
@@ -1796,26 +1972,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>40</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="n">
         <v>2016</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="s">
         <v>29</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>123803</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>1.804509542E-5</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>1.1729312019999999E-3</v>
       </c>
       <c r="H34" t="s">
@@ -1825,26 +2001,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="n">
         <v>2016</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="s">
         <v>29</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>123867</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>9.0225477080000001E-5</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>6.4962343490000002E-4</v>
       </c>
       <c r="H35" t="s">
@@ -1854,26 +2030,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>40</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="n">
         <v>2016</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="s">
         <v>29</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>124929</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>1.804509542E-5</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>1.804509542E-5</v>
       </c>
       <c r="H36" t="s">
@@ -1883,26 +2059,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>40</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="n">
         <v>2016</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="s">
         <v>29</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>138922</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>1.804509542E-5</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>7.7593910289999995E-4</v>
       </c>
       <c r="H37" t="s">
@@ -1912,26 +2088,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>40</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="n">
         <v>2017</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="s">
         <v>29</v>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>100946</v>
       </c>
-      <c r="F38">
+      <c r="F38" t="n">
         <v>4.8420428770000001E-5</v>
       </c>
-      <c r="G38">
+      <c r="G38" t="n">
         <v>2.421021439E-4</v>
       </c>
       <c r="H38" t="s">
@@ -1941,26 +2117,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>40</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="n">
         <v>2017</v>
       </c>
-      <c r="C39">
+      <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="s">
         <v>29</v>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>107236</v>
       </c>
-      <c r="F39">
+      <c r="F39" t="n">
         <v>4.8420428770000001E-5</v>
       </c>
-      <c r="G39">
+      <c r="G39" t="n">
         <v>2.421021439E-4</v>
       </c>
       <c r="H39" t="s">
@@ -1970,26 +2146,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="n">
         <v>2017</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="s">
         <v>29</v>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>107350</v>
       </c>
-      <c r="F40">
+      <c r="F40" t="n">
         <v>1.6140142920000001E-5</v>
       </c>
-      <c r="G40">
+      <c r="G40" t="n">
         <v>3.4669026999999998E-2</v>
       </c>
       <c r="H40" t="s">
@@ -1999,26 +2175,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="n">
         <v>2017</v>
       </c>
-      <c r="C41">
+      <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="s">
         <v>29</v>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>123803</v>
       </c>
-      <c r="F41">
+      <c r="F41" t="n">
         <v>6.4560571699999995E-5</v>
       </c>
-      <c r="G41">
+      <c r="G41" t="n">
         <v>1.7592755790000001E-3</v>
       </c>
       <c r="H41" t="s">
@@ -2028,26 +2204,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="n">
         <v>2017</v>
       </c>
-      <c r="C42">
+      <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="s">
         <v>29</v>
       </c>
-      <c r="E42">
+      <c r="E42" t="n">
         <v>123867</v>
       </c>
-      <c r="F42">
+      <c r="F42" t="n">
         <v>4.8420428770000001E-5</v>
       </c>
-      <c r="G42">
+      <c r="G42" t="n">
         <v>4.8420428770000001E-4</v>
       </c>
       <c r="H42" t="s">
@@ -2057,26 +2233,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>40</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="n">
         <v>2017</v>
       </c>
-      <c r="C43">
+      <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="s">
         <v>29</v>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>124951</v>
       </c>
-      <c r="F43">
+      <c r="F43" t="n">
         <v>1.6140142920000001E-5</v>
       </c>
-      <c r="G43">
+      <c r="G43" t="n">
         <v>1.6140142920000001E-5</v>
       </c>
       <c r="H43" t="s">
@@ -2086,26 +2262,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>40</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="n">
         <v>2017</v>
       </c>
-      <c r="C44">
+      <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="s">
         <v>29</v>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>141101</v>
       </c>
-      <c r="F44">
+      <c r="F44" t="n">
         <v>1.6140142920000001E-5</v>
       </c>
-      <c r="G44">
+      <c r="G44" t="n">
         <v>1.084617605E-2</v>
       </c>
       <c r="H44" t="s">
@@ -2115,26 +2291,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>40</v>
       </c>
-      <c r="B45">
+      <c r="B45" t="n">
         <v>2018</v>
       </c>
-      <c r="C45">
+      <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="s">
         <v>29</v>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>100946</v>
       </c>
-      <c r="F45">
+      <c r="F45" t="n">
         <v>5.4841398680000003E-5</v>
       </c>
-      <c r="G45">
+      <c r="G45" t="n">
         <v>5.4841398679999999E-4</v>
       </c>
       <c r="H45" t="s">
@@ -2144,26 +2320,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" t="s">
         <v>40</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="n">
         <v>2018</v>
       </c>
-      <c r="C46">
+      <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>107236</v>
       </c>
-      <c r="F46">
+      <c r="F46" t="n">
         <v>5.4841398680000003E-5</v>
       </c>
-      <c r="G46">
+      <c r="G46" t="n">
         <v>4.0217025699999998E-4</v>
       </c>
       <c r="H46" t="s">
@@ -2173,26 +2349,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>40</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="n">
         <v>2018</v>
       </c>
-      <c r="C47">
+      <c r="C47" t="n">
         <v>1</v>
       </c>
       <c r="D47" t="s">
         <v>29</v>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>123803</v>
       </c>
-      <c r="F47">
+      <c r="F47" t="n">
         <v>7.3121864900000001E-5</v>
       </c>
-      <c r="G47">
+      <c r="G47" t="n">
         <v>2.8700331970000002E-3</v>
       </c>
       <c r="H47" t="s">
@@ -2202,26 +2378,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>40</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="n">
         <v>2018</v>
       </c>
-      <c r="C48">
+      <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="s">
         <v>29</v>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>123867</v>
       </c>
-      <c r="F48">
+      <c r="F48" t="n">
         <v>9.1402331129999997E-5</v>
       </c>
-      <c r="G48">
+      <c r="G48" t="n">
         <v>8.4090144639999999E-4</v>
       </c>
       <c r="H48" t="s">
@@ -2231,26 +2407,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>40</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="n">
         <v>2018</v>
       </c>
-      <c r="C49">
+      <c r="C49" t="n">
         <v>1</v>
       </c>
       <c r="D49" t="s">
         <v>29</v>
       </c>
-      <c r="E49">
+      <c r="E49" t="n">
         <v>124929</v>
       </c>
-      <c r="F49">
+      <c r="F49" t="n">
         <v>3.6560932450000001E-5</v>
       </c>
-      <c r="G49">
+      <c r="G49" t="n">
         <v>3.6560932450000001E-5</v>
       </c>
       <c r="H49" t="s">
@@ -2260,26 +2436,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>40</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="n">
         <v>2018</v>
       </c>
-      <c r="C50">
+      <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="s">
         <v>29</v>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>138922</v>
       </c>
-      <c r="F50">
+      <c r="F50" t="n">
         <v>3.6560932450000001E-5</v>
       </c>
-      <c r="G50">
+      <c r="G50" t="n">
         <v>7.8606004769999998E-4</v>
       </c>
       <c r="H50" t="s">
@@ -2289,26 +2465,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>40</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="n">
         <v>2018</v>
       </c>
-      <c r="C51">
+      <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="s">
         <v>29</v>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>532031</v>
       </c>
-      <c r="F51">
+      <c r="F51" t="n">
         <v>1.096827974E-4</v>
       </c>
-      <c r="G51">
+      <c r="G51" t="n">
         <v>1.2247912370000001E-2</v>
       </c>
       <c r="H51" t="s">
@@ -2318,26 +2494,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>40</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="n">
         <v>2019</v>
       </c>
-      <c r="C52">
+      <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="s">
         <v>29</v>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>107157</v>
       </c>
-      <c r="F52">
+      <c r="F52" t="n">
         <v>1.812938799E-5</v>
       </c>
-      <c r="G52">
+      <c r="G52" t="n">
         <v>2.1755265590000001E-4</v>
       </c>
       <c r="H52" t="s">
@@ -2347,26 +2523,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>40</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="n">
         <v>2019</v>
       </c>
-      <c r="C53">
+      <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="s">
         <v>29</v>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>123803</v>
       </c>
-      <c r="F53">
+      <c r="F53" t="n">
         <v>1.269057159E-4</v>
       </c>
-      <c r="G53">
+      <c r="G53" t="n">
         <v>5.3662988460000003E-3</v>
       </c>
       <c r="H53" t="s">
@@ -2376,26 +2552,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>40</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="n">
         <v>2019</v>
       </c>
-      <c r="C54">
+      <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="s">
         <v>29</v>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>123867</v>
       </c>
-      <c r="F54">
+      <c r="F54" t="n">
         <v>9.0646939959999998E-5</v>
       </c>
-      <c r="G54">
+      <c r="G54" t="n">
         <v>5.8014041569999996E-4</v>
       </c>
       <c r="H54" t="s">
@@ -2405,26 +2581,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>40</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="n">
         <v>2019</v>
       </c>
-      <c r="C55">
+      <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="s">
         <v>29</v>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>124294</v>
       </c>
-      <c r="F55">
+      <c r="F55" t="n">
         <v>3.6258775980000001E-5</v>
       </c>
-      <c r="G55">
+      <c r="G55" t="n">
         <v>9.9711633949999996E-3</v>
       </c>
       <c r="H55" t="s">
@@ -2434,26 +2610,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>40</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="n">
         <v>2019</v>
       </c>
-      <c r="C56">
+      <c r="C56" t="n">
         <v>1</v>
       </c>
       <c r="D56" t="s">
         <v>29</v>
       </c>
-      <c r="E56">
+      <c r="E56" t="n">
         <v>124929</v>
       </c>
-      <c r="F56">
+      <c r="F56" t="n">
         <v>1.812938799E-5</v>
       </c>
-      <c r="G56">
+      <c r="G56" t="n">
         <v>5.4388163979999997E-5</v>
       </c>
       <c r="H56" t="s">
@@ -2463,26 +2639,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>40</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="n">
         <v>2019</v>
       </c>
-      <c r="C57">
+      <c r="C57" t="n">
         <v>1</v>
       </c>
       <c r="D57" t="s">
         <v>29</v>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>130464</v>
       </c>
-      <c r="F57">
+      <c r="F57" t="n">
         <v>1.812938799E-5</v>
       </c>
-      <c r="G57">
+      <c r="G57" t="n">
         <v>3.6258775980000001E-5</v>
       </c>
       <c r="H57" t="s">
@@ -2492,26 +2668,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>40</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="n">
         <v>2019</v>
       </c>
-      <c r="C58">
+      <c r="C58" t="n">
         <v>1</v>
       </c>
       <c r="D58" t="s">
         <v>29</v>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>532031</v>
       </c>
-      <c r="F58">
+      <c r="F58" t="n">
         <v>3.4445837179999998E-4</v>
       </c>
-      <c r="G58">
+      <c r="G58" t="n">
         <v>0.1017965136</v>
       </c>
       <c r="H58" t="s">
@@ -2521,26 +2697,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>40</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="n">
         <v>2020</v>
       </c>
-      <c r="C59">
+      <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="s">
         <v>29</v>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>100946</v>
       </c>
-      <c r="F59">
+      <c r="F59" t="n">
         <v>7.1897523019999997E-4</v>
       </c>
-      <c r="G59">
+      <c r="G59" t="n">
         <v>2.6961571129999998E-3</v>
       </c>
       <c r="H59" t="s">
@@ -2550,26 +2726,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>40</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="n">
         <v>2020</v>
       </c>
-      <c r="C60">
+      <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="s">
         <v>29</v>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>107236</v>
       </c>
-      <c r="F60">
+      <c r="F60" t="n">
         <v>5.7518018419999999E-4</v>
       </c>
-      <c r="G60">
+      <c r="G60" t="n">
         <v>6.2910332640000004E-3</v>
       </c>
       <c r="H60" t="s">
@@ -2579,26 +2755,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>40</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="n">
         <v>2020</v>
       </c>
-      <c r="C61">
+      <c r="C61" t="n">
         <v>1</v>
       </c>
       <c r="D61" t="s">
         <v>29</v>
       </c>
-      <c r="E61">
+      <c r="E61" t="n">
         <v>107327</v>
       </c>
-      <c r="F61">
+      <c r="F61" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G61">
+      <c r="G61" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
       <c r="H61" t="s">
@@ -2608,26 +2784,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>40</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="n">
         <v>2020</v>
       </c>
-      <c r="C62">
+      <c r="C62" t="n">
         <v>1</v>
       </c>
       <c r="D62" t="s">
         <v>29</v>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>107350</v>
       </c>
-      <c r="F62">
+      <c r="F62" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G62">
+      <c r="G62" t="n">
         <v>1.9771818829999999E-2</v>
       </c>
       <c r="H62" t="s">
@@ -2637,26 +2813,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>40</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="n">
         <v>2020</v>
       </c>
-      <c r="C63">
+      <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="s">
         <v>29</v>
       </c>
-      <c r="E63">
+      <c r="E63" t="n">
         <v>107696</v>
       </c>
-      <c r="F63">
+      <c r="F63" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G63">
+      <c r="G63" t="n">
         <v>3.5948761509999998E-5</v>
       </c>
       <c r="H63" t="s">
@@ -2666,26 +2842,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>40</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="n">
         <v>2020</v>
       </c>
-      <c r="C64">
+      <c r="C64" t="n">
         <v>1</v>
       </c>
       <c r="D64" t="s">
         <v>29</v>
       </c>
-      <c r="E64">
+      <c r="E64" t="n">
         <v>123803</v>
       </c>
-      <c r="F64">
+      <c r="F64" t="n">
         <v>5.3923142270000004E-4</v>
       </c>
-      <c r="G64">
+      <c r="G64" t="n">
         <v>2.6062852099999999E-2</v>
       </c>
       <c r="H64" t="s">
@@ -2695,26 +2871,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>40</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="n">
         <v>2020</v>
       </c>
-      <c r="C65">
+      <c r="C65" t="n">
         <v>1</v>
       </c>
       <c r="D65" t="s">
         <v>29</v>
       </c>
-      <c r="E65">
+      <c r="E65" t="n">
         <v>123851</v>
       </c>
-      <c r="F65">
+      <c r="F65" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G65">
+      <c r="G65" t="n">
         <v>8.9871903779999997E-5</v>
       </c>
       <c r="H65" t="s">
@@ -2724,26 +2900,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>40</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="n">
         <v>2020</v>
       </c>
-      <c r="C66">
+      <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="s">
         <v>29</v>
       </c>
-      <c r="E66">
+      <c r="E66" t="n">
         <v>123867</v>
       </c>
-      <c r="F66">
+      <c r="F66" t="n">
         <v>3.9543637659999998E-4</v>
       </c>
-      <c r="G66">
+      <c r="G66" t="n">
         <v>4.2419538579999997E-3</v>
       </c>
       <c r="H66" t="s">
@@ -2753,26 +2929,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>40</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="n">
         <v>2020</v>
       </c>
-      <c r="C67">
+      <c r="C67" t="n">
         <v>1</v>
       </c>
       <c r="D67" t="s">
         <v>29</v>
       </c>
-      <c r="E67">
+      <c r="E67" t="n">
         <v>124048</v>
       </c>
-      <c r="F67">
+      <c r="F67" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G67">
+      <c r="G67" t="n">
         <v>8.9871903779999997E-5</v>
       </c>
       <c r="H67" t="s">
@@ -2782,26 +2958,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>40</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="n">
         <v>2020</v>
       </c>
-      <c r="C68">
+      <c r="C68" t="n">
         <v>1</v>
       </c>
       <c r="D68" t="s">
         <v>29</v>
       </c>
-      <c r="E68">
+      <c r="E68" t="n">
         <v>124224</v>
       </c>
-      <c r="F68">
+      <c r="F68" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G68">
+      <c r="G68" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
       <c r="H68" t="s">
@@ -2811,26 +2987,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>40</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="n">
         <v>2020</v>
       </c>
-      <c r="C69">
+      <c r="C69" t="n">
         <v>1</v>
       </c>
       <c r="D69" t="s">
         <v>29</v>
       </c>
-      <c r="E69">
+      <c r="E69" t="n">
         <v>124418</v>
       </c>
-      <c r="F69">
+      <c r="F69" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G69">
+      <c r="G69" t="n">
         <v>8.9871903779999997E-5</v>
       </c>
       <c r="H69" t="s">
@@ -2840,26 +3016,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>40</v>
       </c>
-      <c r="B70">
+      <c r="B70" t="n">
         <v>2020</v>
       </c>
-      <c r="C70">
+      <c r="C70" t="n">
         <v>1</v>
       </c>
       <c r="D70" t="s">
         <v>29</v>
       </c>
-      <c r="E70">
+      <c r="E70" t="n">
         <v>128506</v>
       </c>
-      <c r="F70">
+      <c r="F70" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G70">
+      <c r="G70" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
       <c r="H70" t="s">
@@ -2869,26 +3045,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>40</v>
       </c>
-      <c r="B71">
+      <c r="B71" t="n">
         <v>2020</v>
       </c>
-      <c r="C71">
+      <c r="C71" t="n">
         <v>1</v>
       </c>
       <c r="D71" t="s">
         <v>29</v>
       </c>
-      <c r="E71">
+      <c r="E71" t="n">
         <v>129826</v>
       </c>
-      <c r="F71">
+      <c r="F71" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
-      <c r="G71">
+      <c r="G71" t="n">
         <v>1.7974380760000001E-5</v>
       </c>
       <c r="H71" t="s">
@@ -2898,26 +3074,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>40</v>
       </c>
-      <c r="B72">
+      <c r="B72" t="n">
         <v>2020</v>
       </c>
-      <c r="C72">
+      <c r="C72" t="n">
         <v>1</v>
       </c>
       <c r="D72" t="s">
         <v>29</v>
       </c>
-      <c r="E72">
+      <c r="E72" t="n">
         <v>130464</v>
       </c>
-      <c r="F72">
+      <c r="F72" t="n">
         <v>3.5948761509999998E-5</v>
       </c>
-      <c r="G72">
+      <c r="G72" t="n">
         <v>3.5948761509999998E-5</v>
       </c>
       <c r="H72" t="s">
@@ -2927,26 +3103,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>40</v>
       </c>
-      <c r="B73">
+      <c r="B73" t="n">
         <v>2020</v>
       </c>
-      <c r="C73">
+      <c r="C73" t="n">
         <v>1</v>
       </c>
       <c r="D73" t="s">
         <v>29</v>
       </c>
-      <c r="E73">
+      <c r="E73" t="n">
         <v>132511</v>
       </c>
-      <c r="F73">
+      <c r="F73" t="n">
         <v>3.5948761509999998E-5</v>
       </c>
-      <c r="G73">
+      <c r="G73" t="n">
         <v>5.5720580340000003E-4</v>
       </c>
       <c r="H73" t="s">
@@ -2956,26 +3132,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>40</v>
       </c>
-      <c r="B74">
+      <c r="B74" t="n">
         <v>2020</v>
       </c>
-      <c r="C74">
+      <c r="C74" t="n">
         <v>1</v>
       </c>
       <c r="D74" t="s">
         <v>29</v>
       </c>
-      <c r="E74">
+      <c r="E74" t="n">
         <v>141753</v>
       </c>
-      <c r="F74">
+      <c r="F74" t="n">
         <v>3.5948761509999998E-5</v>
       </c>
-      <c r="G74">
+      <c r="G74" t="n">
         <v>8.0884713400000002E-4</v>
       </c>
       <c r="H74" t="s">
@@ -2985,26 +3161,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>40</v>
       </c>
-      <c r="B75">
+      <c r="B75" t="n">
         <v>2020</v>
       </c>
-      <c r="C75">
+      <c r="C75" t="n">
         <v>1</v>
       </c>
       <c r="D75" t="s">
         <v>29</v>
       </c>
-      <c r="E75">
+      <c r="E75" t="n">
         <v>532031</v>
       </c>
-      <c r="F75">
+      <c r="F75" t="n">
         <v>1.9771818829999999E-4</v>
       </c>
-      <c r="G75">
+      <c r="G75" t="n">
         <v>6.2011613610000002E-2</v>
       </c>
       <c r="H75" t="s">
@@ -3014,26 +3190,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>40</v>
       </c>
-      <c r="B76">
+      <c r="B76" t="n">
         <v>2021</v>
       </c>
-      <c r="C76">
+      <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="s">
         <v>29</v>
       </c>
-      <c r="E76">
+      <c r="E76" t="n">
         <v>123803</v>
       </c>
-      <c r="F76">
+      <c r="F76" t="n">
         <v>1.8103368060000002E-5</v>
       </c>
-      <c r="G76">
+      <c r="G76" t="n">
         <v>4.1637746540000001E-4</v>
       </c>
       <c r="H76" t="s">
@@ -3043,26 +3219,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>40</v>
       </c>
-      <c r="B77">
+      <c r="B77" t="n">
         <v>2021</v>
       </c>
-      <c r="C77">
+      <c r="C77" t="n">
         <v>1</v>
       </c>
       <c r="D77" t="s">
         <v>29</v>
       </c>
-      <c r="E77">
+      <c r="E77" t="n">
         <v>123867</v>
       </c>
-      <c r="F77">
+      <c r="F77" t="n">
         <v>1.086202084E-4</v>
       </c>
-      <c r="G77">
+      <c r="G77" t="n">
         <v>1.2310290279999999E-3</v>
       </c>
       <c r="H77" t="s">
@@ -3072,26 +3248,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78" t="s">
         <v>40</v>
       </c>
-      <c r="B78">
+      <c r="B78" t="n">
         <v>2021</v>
       </c>
-      <c r="C78">
+      <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="s">
         <v>29</v>
       </c>
-      <c r="E78">
+      <c r="E78" t="n">
         <v>124048</v>
       </c>
-      <c r="F78">
+      <c r="F78" t="n">
         <v>1.8103368060000002E-5</v>
       </c>
-      <c r="G78">
+      <c r="G78" t="n">
         <v>7.2413472240000004E-4</v>
       </c>
       <c r="H78" t="s">
@@ -3101,26 +3277,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" t="s">
         <v>40</v>
       </c>
-      <c r="B79">
+      <c r="B79" t="n">
         <v>2021</v>
       </c>
-      <c r="C79">
+      <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="s">
         <v>29</v>
       </c>
-      <c r="E79">
+      <c r="E79" t="n">
         <v>532031</v>
       </c>
-      <c r="F79">
+      <c r="F79" t="n">
         <v>1.2672357639999999E-4</v>
       </c>
-      <c r="G79">
+      <c r="G79" t="n">
         <v>4.3086015980000003E-2</v>
       </c>
       <c r="H79" t="s">
@@ -3130,26 +3306,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80" t="s">
         <v>40</v>
       </c>
-      <c r="B80">
+      <c r="B80" t="n">
         <v>2022</v>
       </c>
-      <c r="C80">
+      <c r="C80" t="n">
         <v>1</v>
       </c>
       <c r="D80" t="s">
         <v>29</v>
       </c>
-      <c r="E80">
+      <c r="E80" t="n">
         <v>107342</v>
       </c>
-      <c r="F80">
+      <c r="F80" t="n">
         <v>3.2933477009999999E-5</v>
       </c>
-      <c r="G80">
+      <c r="G80" t="n">
         <v>1.6466738510000001E-5</v>
       </c>
       <c r="H80" t="s">
@@ -3159,26 +3335,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" t="s">
         <v>40</v>
       </c>
-      <c r="B81">
+      <c r="B81" t="n">
         <v>2022</v>
       </c>
-      <c r="C81">
+      <c r="C81" t="n">
         <v>1</v>
       </c>
       <c r="D81" t="s">
         <v>29</v>
       </c>
-      <c r="E81">
+      <c r="E81" t="n">
         <v>123803</v>
       </c>
-      <c r="F81">
+      <c r="F81" t="n">
         <v>4.9400215520000001E-5</v>
       </c>
-      <c r="G81">
+      <c r="G81" t="n">
         <v>8.2663027299999994E-3</v>
       </c>
       <c r="H81" t="s">
@@ -3188,26 +3364,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" t="s">
         <v>40</v>
       </c>
-      <c r="B82">
+      <c r="B82" t="n">
         <v>2022</v>
       </c>
-      <c r="C82">
+      <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="s">
         <v>29</v>
       </c>
-      <c r="E82">
+      <c r="E82" t="n">
         <v>123867</v>
       </c>
-      <c r="F82">
+      <c r="F82" t="n">
         <v>2.3053433909999999E-4</v>
       </c>
-      <c r="G82">
+      <c r="G82" t="n">
         <v>1.9760086210000001E-3</v>
       </c>
       <c r="H82" t="s">
@@ -3217,26 +3393,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" t="s">
         <v>40</v>
       </c>
-      <c r="B83">
+      <c r="B83" t="n">
         <v>2022</v>
       </c>
-      <c r="C83">
+      <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="s">
         <v>29</v>
       </c>
-      <c r="E83">
+      <c r="E83" t="n">
         <v>124287</v>
       </c>
-      <c r="F83">
+      <c r="F83" t="n">
         <v>3.2933477009999999E-5</v>
       </c>
-      <c r="G83">
+      <c r="G83" t="n">
         <v>5.7304249999999999E-3</v>
       </c>
       <c r="H83" t="s">
@@ -3246,26 +3422,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84" t="s">
         <v>40</v>
       </c>
-      <c r="B84">
+      <c r="B84" t="n">
         <v>2022</v>
       </c>
-      <c r="C84">
+      <c r="C84" t="n">
         <v>1</v>
       </c>
       <c r="D84" t="s">
         <v>29</v>
       </c>
-      <c r="E84">
+      <c r="E84" t="n">
         <v>124929</v>
       </c>
-      <c r="F84">
+      <c r="F84" t="n">
         <v>1.6466738510000001E-5</v>
       </c>
-      <c r="G84">
+      <c r="G84" t="n">
         <v>3.2933477009999999E-5</v>
       </c>
       <c r="H84" t="s">
@@ -3275,26 +3451,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85" t="s">
         <v>40</v>
       </c>
-      <c r="B85">
+      <c r="B85" t="n">
         <v>2022</v>
       </c>
-      <c r="C85">
+      <c r="C85" t="n">
         <v>1</v>
       </c>
       <c r="D85" t="s">
         <v>29</v>
       </c>
-      <c r="E85">
+      <c r="E85" t="n">
         <v>141753</v>
       </c>
-      <c r="F85">
+      <c r="F85" t="n">
         <v>1.6466738510000001E-5</v>
       </c>
-      <c r="G85">
+      <c r="G85" t="n">
         <v>4.9400215520000001E-5</v>
       </c>
       <c r="H85" t="s">
@@ -3304,26 +3480,26 @@
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86" t="s">
         <v>40</v>
       </c>
-      <c r="B86">
+      <c r="B86" t="n">
         <v>2022</v>
       </c>
-      <c r="C86">
+      <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="s">
         <v>29</v>
       </c>
-      <c r="E86">
+      <c r="E86" t="n">
         <v>532031</v>
       </c>
-      <c r="F86">
+      <c r="F86" t="n">
         <v>3.1286803160000001E-4</v>
       </c>
-      <c r="G86">
+      <c r="G86" t="n">
         <v>8.318996293E-2</v>
       </c>
       <c r="H86" t="s">
@@ -3340,665 +3516,806 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="19" max="19" width="11.42578125" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="E1" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="F1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="G1" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
       <c r="H1" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="J1" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="K1" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
       <c r="L1" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="M1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="N1" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="O1" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="P1" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="Q1" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="R1" t="s">
-        <v>64</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="S1" t="s">
+        <v>109</v>
+      </c>
+      <c r="T1" t="s">
+        <v>110</v>
+      </c>
+      <c r="U1" t="s">
+        <v>111</v>
+      </c>
+      <c r="V1" t="s">
+        <v>112</v>
+      </c>
+      <c r="W1" t="s">
+        <v>113</v>
+      </c>
+      <c r="X1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2">
-        <v>-4.1239999999999997</v>
-      </c>
-      <c r="E2">
-        <v>43.469333329999998</v>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>89.835418700000005</v>
+        <v>120</v>
+      </c>
+      <c r="D2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-4.124</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.46933333</v>
+      </c>
+      <c r="G2" t="s">
+        <v>122</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I2">
+        <v>123</v>
+      </c>
+      <c r="I2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2"/>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M2" t="s">
+        <v>126</v>
+      </c>
+      <c r="N2"/>
+      <c r="O2" t="n">
+        <v>0.9208281108294</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2" t="n">
+        <v>0.335637149040587</v>
+      </c>
+      <c r="T2" t="n">
         <v>54841.94</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" t="s">
-        <v>71</v>
-      </c>
-      <c r="M2">
-        <v>2.6257276819599999E-2</v>
-      </c>
-      <c r="N2">
-        <v>4.6041405541470001E-2</v>
-      </c>
-      <c r="O2">
-        <v>0.92082811082939997</v>
-      </c>
-      <c r="P2">
-        <v>12</v>
-      </c>
-      <c r="Q2">
-        <v>0.71712573000000002</v>
-      </c>
-      <c r="R2">
+      <c r="U2" t="n">
+        <v>0.0262572768196</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.04604140554147</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.71712573</v>
+      </c>
+      <c r="X2" t="n">
         <v>1.01776168</v>
       </c>
-      <c r="S2" s="1">
-        <v>0.335637149040587</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2" t="n">
+        <v>0.596699669979772</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3">
-        <v>-4.1230000000000002</v>
-      </c>
-      <c r="E3">
-        <v>43.470083330000001</v>
-      </c>
-      <c r="F3">
-        <v>9</v>
-      </c>
-      <c r="G3">
-        <v>89.835418700000005</v>
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-4.123</v>
+      </c>
+      <c r="F3" t="n">
+        <v>43.47008333</v>
+      </c>
+      <c r="G3" t="s">
+        <v>122</v>
       </c>
       <c r="H3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I3">
+        <v>123</v>
+      </c>
+      <c r="I3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="s">
+        <v>125</v>
+      </c>
+      <c r="M3" t="s">
+        <v>126</v>
+      </c>
+      <c r="N3"/>
+      <c r="O3" t="n">
+        <v>0.88680218014563</v>
+      </c>
+      <c r="P3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3" t="n">
+        <v>0.135962330803446</v>
+      </c>
+      <c r="T3" t="n">
         <v>54465.36</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>70</v>
-      </c>
-      <c r="L3" t="s">
-        <v>71</v>
-      </c>
-      <c r="M3">
-        <v>4.588237367616E-2</v>
-      </c>
-      <c r="N3">
-        <v>4.2210314951440002E-2</v>
-      </c>
-      <c r="O3">
-        <v>0.88680218014562995</v>
-      </c>
-      <c r="P3">
-        <v>11</v>
-      </c>
-      <c r="Q3">
-        <v>0.54575885999999996</v>
-      </c>
-      <c r="R3">
-        <v>0.94671495000000006</v>
-      </c>
-      <c r="S3" s="1">
-        <v>0.135962330803446</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="U3" t="n">
+        <v>0.04588237367616</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.04221031495144</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.54575886</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.94671495</v>
+      </c>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3" t="n">
+        <v>0.1744599101382</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4">
+        <v>120</v>
+      </c>
+      <c r="D4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" t="n">
         <v>-4.1185</v>
       </c>
-      <c r="E4">
-        <v>43.470750000000002</v>
-      </c>
-      <c r="F4">
-        <v>9</v>
-      </c>
-      <c r="G4">
-        <v>89.063255310000002</v>
+      <c r="F4" t="n">
+        <v>43.47075</v>
+      </c>
+      <c r="G4" t="s">
+        <v>122</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I4">
+        <v>133</v>
+      </c>
+      <c r="I4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="s">
+        <v>125</v>
+      </c>
+      <c r="M4" t="s">
+        <v>134</v>
+      </c>
+      <c r="N4"/>
+      <c r="O4" t="n">
+        <v>0.22086276494031</v>
+      </c>
+      <c r="P4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4" t="n">
+        <v>0.00291545189467344</v>
+      </c>
+      <c r="T4" t="n">
         <v>55496</v>
       </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4" t="s">
-        <v>70</v>
-      </c>
-      <c r="L4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M4">
-        <v>3.9822689925699999E-3</v>
-      </c>
-      <c r="N4">
-        <v>1.2991927349429999E-2</v>
-      </c>
-      <c r="O4">
-        <v>0.22086276494031001</v>
-      </c>
-      <c r="P4">
+      <c r="U4" t="n">
+        <v>0.00398226899257</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.01299192734943</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.18318618</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.8290444</v>
+      </c>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4" t="n">
+        <v>0.815972222267291</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-4.12675</v>
+      </c>
+      <c r="F5" t="n">
+        <v>43.4685</v>
+      </c>
+      <c r="G5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J5"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>125</v>
+      </c>
+      <c r="M5" t="s">
+        <v>126</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5" t="n">
+        <v>0.05196987479552</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>55416.72</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.00346465832</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.00324811717472</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.08631282</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.50382406</v>
+      </c>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5" t="n">
+        <v>0.390277777789614</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-4.123083333</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.4725</v>
+      </c>
+      <c r="G6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" t="s">
+        <v>124</v>
+      </c>
+      <c r="J6"/>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="s">
+        <v>125</v>
+      </c>
+      <c r="M6" t="s">
+        <v>126</v>
+      </c>
+      <c r="N6"/>
+      <c r="O6" t="n">
+        <v>0.7238854102113</v>
+      </c>
+      <c r="P6" t="n">
         <v>7</v>
       </c>
-      <c r="Q4">
-        <v>1.1831861800000001</v>
-      </c>
-      <c r="R4">
-        <v>0.82904440000000001</v>
-      </c>
-      <c r="S4" s="1">
-        <v>2.9154518946734398E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5">
-        <v>-4.1267500000000004</v>
-      </c>
-      <c r="E5">
-        <v>43.468499999999999</v>
-      </c>
-      <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>89.835418700000005</v>
-      </c>
-      <c r="H5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5">
-        <v>55416.72</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5" t="s">
-        <v>70</v>
-      </c>
-      <c r="L5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5">
-        <v>3.4646583199999998E-3</v>
-      </c>
-      <c r="N5">
-        <v>3.2481171747200002E-3</v>
-      </c>
-      <c r="O5">
-        <v>5.1969874795520003E-2</v>
-      </c>
-      <c r="P5">
-        <v>6</v>
-      </c>
-      <c r="Q5">
-        <v>1.0863128200000001</v>
-      </c>
-      <c r="R5">
-        <v>1.5038240599999999</v>
-      </c>
-      <c r="S5" s="1">
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6">
-        <v>-4.1230833330000003</v>
-      </c>
-      <c r="E6">
-        <v>43.472499999999997</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>89.835418700000005</v>
-      </c>
-      <c r="H6" t="s">
-        <v>69</v>
-      </c>
-      <c r="I6">
+      <c r="T6" t="n">
         <v>61957.32</v>
       </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6" t="s">
-        <v>71</v>
-      </c>
-      <c r="M6">
-        <v>3.8736343015500002E-3</v>
-      </c>
-      <c r="N6">
-        <v>4.8259027347419998E-2</v>
-      </c>
-      <c r="O6">
-        <v>0.72388541021130004</v>
-      </c>
-      <c r="P6">
+      <c r="U6" t="n">
+        <v>0.00387363430155</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.04825902734742</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06158544</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.54840616</v>
+      </c>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6" t="n">
+        <v>0.252090301088515</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-4.124416667</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43.46833333</v>
+      </c>
+      <c r="G7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7" t="s">
+        <v>124</v>
+      </c>
+      <c r="J7"/>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>125</v>
+      </c>
+      <c r="M7" t="s">
+        <v>126</v>
+      </c>
+      <c r="N7"/>
+      <c r="O7" t="n">
+        <v>0.2482487313229</v>
+      </c>
+      <c r="P7" t="n">
         <v>7</v>
       </c>
-      <c r="Q6">
-        <v>1.06158544</v>
-      </c>
-      <c r="R6">
-        <v>0.54840615999999998</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7">
-        <v>-4.1244166670000002</v>
-      </c>
-      <c r="E7">
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7" t="n">
+        <v>0.712765957442568</v>
+      </c>
+      <c r="T7" t="n">
+        <v>54703.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.00639816317966</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.01773205223735</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.66280371</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.73936192</v>
+      </c>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7" t="n">
+        <v>0.373797250850938</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-4.1255</v>
+      </c>
+      <c r="F8" t="n">
         <v>43.46833333</v>
       </c>
-      <c r="F7">
-        <v>9</v>
-      </c>
-      <c r="G7">
-        <v>89.835418700000005</v>
-      </c>
-      <c r="H7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I7">
-        <v>54703.199999999997</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L7" t="s">
-        <v>71</v>
-      </c>
-      <c r="M7">
-        <v>6.3981631796599997E-3</v>
-      </c>
-      <c r="N7">
-        <v>1.7732052237349999E-2</v>
-      </c>
-      <c r="O7">
-        <v>0.24824873132290001</v>
-      </c>
-      <c r="P7">
+      <c r="G8" t="s">
+        <v>122</v>
+      </c>
+      <c r="H8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I8" t="s">
+        <v>124</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>125</v>
+      </c>
+      <c r="M8" t="s">
+        <v>126</v>
+      </c>
+      <c r="N8"/>
+      <c r="O8" t="n">
+        <v>2.00637936949352</v>
+      </c>
+      <c r="P8" t="n">
         <v>7</v>
       </c>
-      <c r="Q7">
-        <v>0.66280371000000005</v>
-      </c>
-      <c r="R7">
-        <v>0.73936192000000001</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0.71276595744256799</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8">
-        <v>-4.1254999999999997</v>
-      </c>
-      <c r="E8">
-        <v>43.46833333</v>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>89.835418700000005</v>
-      </c>
-      <c r="H8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I8">
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8" t="n">
+        <v>0.862519201259954</v>
+      </c>
+      <c r="T8" t="n">
         <v>55159.06</v>
       </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M8">
-        <v>1.109518544937E-2</v>
-      </c>
-      <c r="N8">
+      <c r="U8" t="n">
+        <v>0.01109518544937</v>
+      </c>
+      <c r="V8" t="n">
         <v>0.11802231585256</v>
       </c>
-      <c r="O8">
-        <v>2.0063793694935201</v>
-      </c>
-      <c r="P8">
+      <c r="W8" t="n">
+        <v>0.53689696</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.44560851</v>
+      </c>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8" t="n">
+        <v>0.321607782903683</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-4.12525</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.46783333</v>
+      </c>
+      <c r="G9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" t="s">
+        <v>123</v>
+      </c>
+      <c r="I9" t="s">
+        <v>124</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>125</v>
+      </c>
+      <c r="M9" t="s">
+        <v>126</v>
+      </c>
+      <c r="N9"/>
+      <c r="O9" t="n">
+        <v>3.4399369891544</v>
+      </c>
+      <c r="P9" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9" t="n">
+        <v>0.516828721019537</v>
+      </c>
+      <c r="T9" t="n">
+        <v>55634.74</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.07549239917436</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1228548924698</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.81524368</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.17837744</v>
+      </c>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9" t="n">
+        <v>0.330090221918258</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-4.12425</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.46791667</v>
+      </c>
+      <c r="G10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="s">
+        <v>125</v>
+      </c>
+      <c r="M10" t="s">
+        <v>126</v>
+      </c>
+      <c r="N10"/>
+      <c r="O10" t="n">
+        <v>0.4091180147622</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10" t="n">
+        <v>0.963759458382154</v>
+      </c>
+      <c r="T10" t="n">
+        <v>55238.34</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.00244395468828</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.0454575571958</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.50409312</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.27849947</v>
+      </c>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10" t="n">
+        <v>0.328122925793618</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-4.119083333</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.46991667</v>
+      </c>
+      <c r="G11" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I11" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>125</v>
+      </c>
+      <c r="M11" t="s">
+        <v>134</v>
+      </c>
+      <c r="N11"/>
+      <c r="O11" t="n">
+        <v>1.38966099596856</v>
+      </c>
+      <c r="P11" t="n">
         <v>7</v>
       </c>
-      <c r="Q8">
-        <v>0.53689695999999998</v>
-      </c>
-      <c r="R8">
-        <v>0.44560851000000001</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0.86251920125995396</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9">
-        <v>-4.1252500000000003</v>
-      </c>
-      <c r="E9">
-        <v>43.467833329999998</v>
-      </c>
-      <c r="F9">
-        <v>9</v>
-      </c>
-      <c r="G9">
-        <v>89.835418700000005</v>
-      </c>
-      <c r="H9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9">
-        <v>55634.74</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="L9" t="s">
-        <v>71</v>
-      </c>
-      <c r="M9">
-        <v>7.549239917436E-2</v>
-      </c>
-      <c r="N9">
-        <v>0.1228548924698</v>
-      </c>
-      <c r="O9">
-        <v>3.4399369891544</v>
-      </c>
-      <c r="P9">
-        <v>17</v>
-      </c>
-      <c r="Q9">
-        <v>0.81524368000000003</v>
-      </c>
-      <c r="R9">
-        <v>1.17837744</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0.51682872101953703</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10">
-        <v>-4.12425</v>
-      </c>
-      <c r="E10">
-        <v>43.467916670000001</v>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>89.835418700000005</v>
-      </c>
-      <c r="H10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10">
-        <v>55238.34</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10" t="s">
-        <v>70</v>
-      </c>
-      <c r="L10" t="s">
-        <v>71</v>
-      </c>
-      <c r="M10">
-        <v>2.4439546882800002E-3</v>
-      </c>
-      <c r="N10">
-        <v>4.5457557195799997E-2</v>
-      </c>
-      <c r="O10">
-        <v>0.4091180147622</v>
-      </c>
-      <c r="P10">
-        <v>4</v>
-      </c>
-      <c r="Q10">
-        <v>0.50409311999999995</v>
-      </c>
-      <c r="R10">
-        <v>0.27849947000000003</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0.96375945838215404</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11">
-        <v>-4.1190833329999998</v>
-      </c>
-      <c r="E11">
-        <v>43.469916670000003</v>
-      </c>
-      <c r="F11">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>89.063255310000002</v>
-      </c>
-      <c r="H11" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11">
-        <v>60728.480000000003</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L11" t="s">
-        <v>76</v>
-      </c>
-      <c r="M11">
-        <v>9.6824422416400008E-3</v>
-      </c>
-      <c r="N11">
-        <v>9.9261499712039999E-2</v>
-      </c>
-      <c r="O11">
-        <v>1.38966099596856</v>
-      </c>
-      <c r="P11">
-        <v>7</v>
-      </c>
-      <c r="Q11">
-        <v>0.52080568999999999</v>
-      </c>
-      <c r="R11">
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11" t="n">
+        <v>0.838088918375564</v>
+      </c>
+      <c r="T11" t="n">
+        <v>60728.48</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.00968244224164</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.09926149971204</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.52080569</v>
+      </c>
+      <c r="X11" t="n">
         <v>0.46238667</v>
       </c>
-      <c r="S11" s="1">
-        <v>0.83808891837556398</v>
+      <c r="Y11"/>
+      <c r="Z11"/>
+      <c r="AA11" t="n">
+        <v>0.341821499667688</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4132,13 +4449,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC256C98-E6D2-474A-B693-9A14E444C1B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAD4900E-7216-4504-B91A-05F9D29B2C8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5A88817-429A-48E6-B550-4EC7132F6097}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D03FFB4-3F2E-424B-8B9B-D30872507EE1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{662AA797-4C84-4488-9BD3-2C5C8527F7FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A5CAACC-BAB4-45E1-836E-4721E1A795F0}"/>
 </file>